--- a/LoanOfficer-A/2023/87 Sandhyarani.xlsx
+++ b/LoanOfficer-A/2023/87 Sandhyarani.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="G2" s="21">
         <f>B3+G1-1</f>
-        <v>119</v>
+        <v>45754</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>12000</v>
+        <v>10400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -862,9 +862,15 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="3">
+        <v>45635</v>
+      </c>
+      <c r="C3" s="4">
+        <v>100</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
       <c r="E3" s="1">
         <v>31</v>
       </c>
@@ -888,9 +894,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45635</v>
+      </c>
+      <c r="C4" s="4">
+        <v>100</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -914,9 +926,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45640</v>
+      </c>
+      <c r="C5" s="4">
+        <v>100</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -940,9 +958,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45640</v>
+      </c>
+      <c r="C6" s="4">
+        <v>100</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -966,9 +990,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45640</v>
+      </c>
+      <c r="C7" s="4">
+        <v>100</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -992,9 +1022,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45640</v>
+      </c>
+      <c r="C8" s="4">
+        <v>100</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1018,9 +1054,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45640</v>
+      </c>
+      <c r="C9" s="4">
+        <v>100</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1044,9 +1086,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45643</v>
+      </c>
+      <c r="C10" s="4">
+        <v>100</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1070,9 +1118,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45643</v>
+      </c>
+      <c r="C11" s="4">
+        <v>100</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1096,9 +1150,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45643</v>
+      </c>
+      <c r="C12" s="4">
+        <v>100</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1122,9 +1182,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45645</v>
+      </c>
+      <c r="C13" s="4">
+        <v>100</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1148,9 +1214,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45645</v>
+      </c>
+      <c r="C14" s="4">
+        <v>100</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1174,9 +1246,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45647</v>
+      </c>
+      <c r="C15" s="4">
+        <v>100</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1200,9 +1278,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45647</v>
+      </c>
+      <c r="C16" s="4">
+        <v>100</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1226,9 +1310,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45649</v>
+      </c>
+      <c r="C17" s="4">
+        <v>100</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1252,9 +1342,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45649</v>
+      </c>
+      <c r="C18" s="4">
+        <v>100</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>

--- a/LoanOfficer-A/2023/87 Sandhyarani.xlsx
+++ b/LoanOfficer-A/2023/87 Sandhyarani.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>10400</v>
+        <v>9900</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1374,9 +1374,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45651</v>
+      </c>
+      <c r="C19" s="4">
+        <v>100</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1400,9 +1406,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45651</v>
+      </c>
+      <c r="C20" s="4">
+        <v>100</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1426,9 +1438,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45654</v>
+      </c>
+      <c r="C21" s="4">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1452,9 +1470,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45654</v>
+      </c>
+      <c r="C22" s="4">
+        <v>100</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1478,9 +1502,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45654</v>
+      </c>
+      <c r="C23" s="4">
+        <v>100</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>

--- a/LoanOfficer-A/2023/87 Sandhyarani.xlsx
+++ b/LoanOfficer-A/2023/87 Sandhyarani.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>2100</v>
+        <v>4100</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>9900</v>
+        <v>7900</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -874,9 +874,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G3" s="4">
+        <v>100</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -906,9 +912,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G4" s="4">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -938,9 +950,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G5" s="4">
+        <v>100</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -970,9 +988,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G6" s="4">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1002,9 +1026,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G7" s="4">
+        <v>100</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1034,9 +1064,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1066,9 +1102,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45673</v>
+      </c>
+      <c r="G9" s="4">
+        <v>100</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1098,9 +1140,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45673</v>
+      </c>
+      <c r="G10" s="4">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1130,9 +1178,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45675</v>
+      </c>
+      <c r="G11" s="4">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1162,9 +1216,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45675</v>
+      </c>
+      <c r="G12" s="4">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1194,9 +1254,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45675</v>
+      </c>
+      <c r="G13" s="4">
+        <v>100</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1534,9 +1600,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45670</v>
+      </c>
+      <c r="C24" s="4">
+        <v>100</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1560,9 +1632,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45670</v>
+      </c>
+      <c r="C25" s="4">
+        <v>100</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1586,9 +1664,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45670</v>
+      </c>
+      <c r="C26" s="4">
+        <v>100</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1612,9 +1696,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45670</v>
+      </c>
+      <c r="C27" s="4">
+        <v>100</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1638,9 +1728,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45670</v>
+      </c>
+      <c r="C28" s="4">
+        <v>100</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1664,9 +1760,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45670</v>
+      </c>
+      <c r="C29" s="4">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1690,9 +1792,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45670</v>
+      </c>
+      <c r="C30" s="4">
+        <v>100</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1716,9 +1824,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45670</v>
+      </c>
+      <c r="C31" s="4">
+        <v>100</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1742,9 +1856,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45670</v>
+      </c>
+      <c r="C32" s="4">
+        <v>100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/87 Sandhyarani.xlsx
+++ b/LoanOfficer-A/2023/87 Sandhyarani.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4100</v>
+        <v>5700</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>7900</v>
+        <v>6300</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1292,9 +1292,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45678</v>
+      </c>
+      <c r="G14" s="4">
+        <v>100</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1324,9 +1330,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45678</v>
+      </c>
+      <c r="G15" s="4">
+        <v>100</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1356,9 +1368,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45680</v>
+      </c>
+      <c r="G16" s="4">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1388,9 +1406,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45680</v>
+      </c>
+      <c r="G17" s="4">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1420,9 +1444,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45683</v>
+      </c>
+      <c r="G18" s="4">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1452,9 +1482,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45683</v>
+      </c>
+      <c r="G19" s="4">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1484,9 +1520,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45683</v>
+      </c>
+      <c r="G20" s="4">
+        <v>100</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1516,9 +1558,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45689</v>
+      </c>
+      <c r="G21" s="4">
+        <v>100</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1548,9 +1596,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45689</v>
+      </c>
+      <c r="G22" s="4">
+        <v>100</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1580,9 +1634,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45689</v>
+      </c>
+      <c r="G23" s="4">
+        <v>100</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1612,9 +1672,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45691</v>
+      </c>
+      <c r="G24" s="4">
+        <v>100</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1644,9 +1710,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45691</v>
+      </c>
+      <c r="G25" s="4">
+        <v>100</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1676,9 +1748,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45691</v>
+      </c>
+      <c r="G26" s="4">
+        <v>100</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1708,9 +1786,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45691</v>
+      </c>
+      <c r="G27" s="4">
+        <v>100</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1740,9 +1824,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45691</v>
+      </c>
+      <c r="G28" s="4">
+        <v>100</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1772,9 +1862,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45692</v>
+      </c>
+      <c r="G29" s="4">
+        <v>100</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>

--- a/LoanOfficer-A/2023/87 Sandhyarani.xlsx
+++ b/LoanOfficer-A/2023/87 Sandhyarani.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>5700</v>
+        <v>6300</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>6300</v>
+        <v>5700</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45698</v>
+      </c>
+      <c r="K3" s="4">
+        <v>100</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -924,9 +930,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45698</v>
+      </c>
+      <c r="K4" s="4">
+        <v>100</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -962,9 +974,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>45698</v>
+      </c>
+      <c r="K5" s="4">
+        <v>100</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
@@ -1900,9 +1918,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45698</v>
+      </c>
+      <c r="G30" s="4">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1932,9 +1956,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45698</v>
+      </c>
+      <c r="G31" s="4">
+        <v>100</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1964,9 +1994,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45698</v>
+      </c>
+      <c r="G32" s="4">
+        <v>100</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>

--- a/LoanOfficer-A/2023/87 Sandhyarani.xlsx
+++ b/LoanOfficer-A/2023/87 Sandhyarani.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>6300</v>
+        <v>7600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5700</v>
+        <v>4400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1018,9 +1018,15 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K6" s="4">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>
@@ -1056,9 +1062,15 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K7" s="4">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
@@ -1094,9 +1106,15 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K8" s="4">
+        <v>100</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
@@ -1132,9 +1150,15 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K9" s="4">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
@@ -1170,9 +1194,15 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K10" s="4">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>
@@ -1208,9 +1238,15 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K11" s="4">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>
@@ -1246,9 +1282,15 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K12" s="4">
+        <v>100</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
@@ -1284,9 +1326,15 @@
       <c r="I13" s="1">
         <v>71</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>45706</v>
+      </c>
+      <c r="K13" s="4">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
       <c r="M13" s="1">
         <v>101</v>
       </c>
@@ -1322,9 +1370,15 @@
       <c r="I14" s="1">
         <v>72</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="3">
+        <v>45710</v>
+      </c>
+      <c r="K14" s="4">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
       <c r="M14" s="1">
         <v>102</v>
       </c>
@@ -1360,9 +1414,15 @@
       <c r="I15" s="1">
         <v>73</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="3">
+        <v>45710</v>
+      </c>
+      <c r="K15" s="4">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
       <c r="M15" s="1">
         <v>103</v>
       </c>
@@ -1398,9 +1458,15 @@
       <c r="I16" s="1">
         <v>74</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="3">
+        <v>45710</v>
+      </c>
+      <c r="K16" s="4">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
       <c r="M16" s="1">
         <v>104</v>
       </c>
@@ -1436,9 +1502,15 @@
       <c r="I17" s="1">
         <v>75</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="3">
+        <v>45710</v>
+      </c>
+      <c r="K17" s="4">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
       <c r="M17" s="1">
         <v>105</v>
       </c>
@@ -1474,9 +1546,15 @@
       <c r="I18" s="1">
         <v>76</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>45710</v>
+      </c>
+      <c r="K18" s="4">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
       <c r="M18" s="1">
         <v>106</v>
       </c>

--- a/LoanOfficer-A/2023/87 Sandhyarani.xlsx
+++ b/LoanOfficer-A/2023/87 Sandhyarani.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7600</v>
+        <v>8300</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>4400</v>
+        <v>3700</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1590,9 +1590,15 @@
       <c r="I19" s="1">
         <v>77</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="3">
+        <v>45714</v>
+      </c>
+      <c r="K19" s="4">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
@@ -1628,9 +1634,15 @@
       <c r="I20" s="1">
         <v>78</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="3">
+        <v>45714</v>
+      </c>
+      <c r="K20" s="4">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
       <c r="M20" s="1">
         <v>108</v>
       </c>
@@ -1666,9 +1678,15 @@
       <c r="I21" s="1">
         <v>79</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
+      <c r="J21" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K21" s="4">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
       <c r="M21" s="1">
         <v>109</v>
       </c>
@@ -1704,9 +1722,15 @@
       <c r="I22" s="1">
         <v>80</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
+      <c r="J22" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K22" s="4">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
       <c r="M22" s="1">
         <v>110</v>
       </c>
@@ -1742,9 +1766,15 @@
       <c r="I23" s="1">
         <v>81</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
+      <c r="J23" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K23" s="4">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
       <c r="M23" s="1">
         <v>111</v>
       </c>
@@ -1780,9 +1810,15 @@
       <c r="I24" s="1">
         <v>82</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
+      <c r="J24" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K24" s="4">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
       <c r="M24" s="1">
         <v>112</v>
       </c>
@@ -1818,9 +1854,15 @@
       <c r="I25" s="1">
         <v>83</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
+      <c r="J25" s="3">
+        <v>45719</v>
+      </c>
+      <c r="K25" s="4">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
       <c r="M25" s="1">
         <v>113</v>
       </c>
